--- a/Outputs/Tables/T3.xlsx
+++ b/Outputs/Tables/T3.xlsx
@@ -23,7 +23,7 @@
     <t xml:space="preserve">FTC</t>
   </si>
   <si>
-    <t xml:space="preserve">FV-PTC</t>
+    <t xml:space="preserve">IEFVPTC</t>
   </si>
   <si>
     <t xml:space="preserve">PTC</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">0.005</t>
   </si>
   <si>
-    <t xml:space="preserve">o-Toluidineᵃ</t>
+    <t xml:space="preserve">o-Toluidine†</t>
   </si>
   <si>
     <t xml:space="preserve">Dye Intermediate</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.56ᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26ᵈ</t>
+    <t xml:space="preserve">-0.56ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26ᵃ</t>
   </si>
   <si>
     <t xml:space="preserve">0.007</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">20%</t>
   </si>
   <si>
-    <t xml:space="preserve">DNOPᵇ</t>
+    <t xml:space="preserve">DNOP‡</t>
   </si>
   <si>
     <t xml:space="preserve">Plasticizer</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.25ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.30ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56ᵉ</t>
+    <t xml:space="preserve">-0.25ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.30ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56ᵇ</t>
   </si>
   <si>
     <t xml:space="preserve">0.008</t>
@@ -119,31 +119,31 @@
     <t xml:space="preserve">2,4-Dimethylphenol</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.36ᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.18ᵉ</t>
+    <t xml:space="preserve">-0.36ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.18ᵇ</t>
   </si>
   <si>
     <t xml:space="preserve">0.009</t>
   </si>
   <si>
-    <t xml:space="preserve">MEHPᵇ</t>
+    <t xml:space="preserve">MEHP‡</t>
   </si>
   <si>
     <t xml:space="preserve">Plasticizer Metabolite</t>
   </si>
   <si>
-    <t xml:space="preserve">0.06ᵈᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.50ᵉ</t>
+    <t xml:space="preserve">0.06ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.50ᵇ</t>
   </si>
   <si>
     <t xml:space="preserve">Acetophenone</t>
@@ -158,34 +158,34 @@
     <t xml:space="preserve">0.011</t>
   </si>
   <si>
-    <t xml:space="preserve">Fluorantheneᵇ</t>
+    <t xml:space="preserve">Fluoranthene‡</t>
   </si>
   <si>
     <t xml:space="preserve">Combustion Byproduct (PAH)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.34ᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.18ᵈᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52ᵈ</t>
+    <t xml:space="preserve">-0.34ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.18ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52ᵃ</t>
   </si>
   <si>
     <t xml:space="preserve">0.012</t>
   </si>
   <si>
-    <t xml:space="preserve">Menthoneᶜ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.40ᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.10ᵈᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49ᵈ</t>
+    <t xml:space="preserve">Menthone¶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.40ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.10ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49ᵃ</t>
   </si>
   <si>
     <t xml:space="preserve">0.014</t>
@@ -194,19 +194,19 @@
     <t xml:space="preserve">Pyrene</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.09ᵈᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.38ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47ᵉ</t>
+    <t xml:space="preserve">-0.09ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.38ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47ᵇ</t>
   </si>
   <si>
     <t xml:space="preserve">0.022</t>
   </si>
   <si>
-    <t xml:space="preserve">Methoxychlorᵃᵇ</t>
+    <t xml:space="preserve">Methoxychlor†‡</t>
   </si>
   <si>
     <t xml:space="preserve">90%</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">0.023</t>
   </si>
   <si>
-    <t xml:space="preserve">TTBNPᵇ</t>
+    <t xml:space="preserve">TTBNP‡</t>
   </si>
   <si>
     <t xml:space="preserve">Flame Retardant (Brominated)</t>
@@ -233,58 +233,58 @@
     <t xml:space="preserve">Ethyl butyrate</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48ᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.19ᵈᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.29ᵈ</t>
+    <t xml:space="preserve">0.48ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.19ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.29ᵃ</t>
   </si>
   <si>
     <t xml:space="preserve">0.027</t>
   </si>
   <si>
-    <t xml:space="preserve">Benz(a)anthraceneᵃᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.30ᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.17ᵈᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48ᵈ</t>
+    <t xml:space="preserve">Benz(a)anthracene†‡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.30ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.17ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48ᵃ</t>
   </si>
   <si>
     <t xml:space="preserve">0.028</t>
   </si>
   <si>
-    <t xml:space="preserve">N-MeFOSAAᵃ</t>
+    <t xml:space="preserve">N-MeFOSAA†</t>
   </si>
   <si>
     <t xml:space="preserve">PFAS</t>
   </si>
   <si>
-    <t xml:space="preserve">0.07ᵈᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.45ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38ᵉ</t>
+    <t xml:space="preserve">0.07ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.45ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38ᵇ</t>
   </si>
   <si>
     <t xml:space="preserve">0.029</t>
   </si>
   <si>
-    <t xml:space="preserve">Terbuthylazineᵇ</t>
+    <t xml:space="preserve">Terbuthylazine‡</t>
   </si>
   <si>
     <t xml:space="preserve">Herbicide (Triazine)</t>
   </si>
   <si>
-    <t xml:space="preserve">MDAᵃᵇᶜ</t>
+    <t xml:space="preserve">MDA†‡¶</t>
   </si>
   <si>
     <t xml:space="preserve">0.030</t>
@@ -296,28 +296,28 @@
     <t xml:space="preserve">Insecticide/Pesticide (Organophosphate)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.09ᵈᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36ᵉ</t>
+    <t xml:space="preserve">0.09ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36ᵇ</t>
   </si>
   <si>
     <t xml:space="preserve">0.031</t>
   </si>
   <si>
-    <t xml:space="preserve">5-NOTᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.47ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21ᵈ</t>
+    <t xml:space="preserve">5-NOT†</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.47ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21ᵃ</t>
   </si>
   <si>
     <t xml:space="preserve">0.035</t>
   </si>
   <si>
-    <t xml:space="preserve">Dibutyl phthalateᵇᶜ</t>
+    <t xml:space="preserve">Dibutyl phthalate‡¶</t>
   </si>
   <si>
     <t xml:space="preserve">45%</t>
@@ -329,28 +329,28 @@
     <t xml:space="preserve">0.036</t>
   </si>
   <si>
-    <t xml:space="preserve">o-aminoazotolueneᵃᵇᶜ</t>
+    <t xml:space="preserve">o-aminoazotoluene†‡¶</t>
   </si>
   <si>
     <t xml:space="preserve">0.039</t>
   </si>
   <si>
-    <t xml:space="preserve">OD-PABAᵇ</t>
+    <t xml:space="preserve">OD-PABA‡</t>
   </si>
   <si>
     <t xml:space="preserve">Organic UV Filter</t>
   </si>
   <si>
-    <t xml:space="preserve">Prosulfuronᵇ</t>
+    <t xml:space="preserve">Prosulfuron‡</t>
   </si>
   <si>
     <t xml:space="preserve">Herbicide (Sulfonylurea)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.28ᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46ᵈ</t>
+    <t xml:space="preserve">-0.28ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46ᵃ</t>
   </si>
   <si>
     <t xml:space="preserve">DEET</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">Insecticide/Pesticide (Insect Repellent)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.46ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23ᵈ</t>
+    <t xml:space="preserve">-0.46ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23ᵃ</t>
   </si>
   <si>
     <t xml:space="preserve">Hexanoic acid</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">0.042</t>
   </si>
   <si>
-    <t xml:space="preserve">Metalaxylᵇ</t>
+    <t xml:space="preserve">Metalaxyl‡</t>
   </si>
   <si>
     <t xml:space="preserve">Fungicide (Other)</t>
@@ -389,28 +389,28 @@
     <t xml:space="preserve">Insecticide/Pesticide (Pyrethroid)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.24ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.21ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.45ᵈ</t>
+    <t xml:space="preserve">-0.24ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.21ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.45ᵃ</t>
   </si>
   <si>
     <t xml:space="preserve">0.046</t>
   </si>
   <si>
-    <t xml:space="preserve">Anthraceneᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10ᵈᵉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32ᵈ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.43ᵉ</t>
+    <t xml:space="preserve">Anthracene†</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.43ᵇ</t>
   </si>
   <si>
     <t xml:space="preserve">0.049</t>
@@ -419,9 +419,9 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">ᵃ Possible, likely, or known carcinogen
-ᵇ Potential endocrine disrupting chemical
-ᶜ Indicates level 2 identification
+    <t xml:space="preserve">† Possible, likely, or known carcinogen
+‡ Potential endocrine disrupting chemical
+¶ Indicates level 2 identification
 Abbreviations: 5-NOT = 5-Nitro-o-toluidine; DEET = N,N-Diethyl-meta-toluamide; DNOP = Di-n-octyl phthalate; MDA = 4,4'-Diaminodiphenylmethane; MEHP = Mono-2-ethylhexyl phthalate; N-MeFOSAA = N-Methylperfluoro-1-octanesulfonamidoacetic acid (linear); OD-PABA = Octyl-dimethyl-p-aminobenzoic acid; PAH = polycyclic aromatic hydrocarbon; TEEP = Tetraethyl ethylenediphosphonate; TTBNP = Tris(tribromoneopentyl); UV = ultraviolet</t>
   </si>
 </sst>

--- a/Outputs/Tables/T3.xlsx
+++ b/Outputs/Tables/T3.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">PTC</t>
   </si>
   <si>
-    <t xml:space="preserve">p-value</t>
+    <t xml:space="preserve">P value</t>
   </si>
   <si>
     <t xml:space="preserve">Ethylan</t>
@@ -514,9 +514,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Outputs/Tables/T3.xlsx
+++ b/Outputs/Tables/T3.xlsx
@@ -329,7 +329,7 @@
     <t xml:space="preserve">0.036</t>
   </si>
   <si>
-    <t xml:space="preserve">o-aminoazotoluene†‡¶</t>
+    <t xml:space="preserve">o-Aminoazotoluene†‡¶</t>
   </si>
   <si>
     <t xml:space="preserve">0.039</t>

--- a/Outputs/Tables/T3.xlsx
+++ b/Outputs/Tables/T3.xlsx
@@ -329,7 +329,7 @@
     <t xml:space="preserve">0.036</t>
   </si>
   <si>
-    <t xml:space="preserve">o-Aminoazotoluene†‡¶</t>
+    <t xml:space="preserve">o-aminoazotoluene†‡¶</t>
   </si>
   <si>
     <t xml:space="preserve">0.039</t>

--- a/Outputs/Tables/T3.xlsx
+++ b/Outputs/Tables/T3.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t xml:space="preserve">Chemical Name</t>
   </si>
@@ -215,157 +215,148 @@
     <t xml:space="preserve">0.023</t>
   </si>
   <si>
-    <t xml:space="preserve">TTBNP‡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flame Retardant (Brominated)</t>
+    <t xml:space="preserve">Ethyl butyrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.19ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.29ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benz(a)anthracene†‡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.30ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.17ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-MeFOSAA†</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.45ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terbuthylazine‡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbicide (Triazine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDA†‡¶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insecticide/Pesticide (Organophosphate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09ᵃᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.36ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-NOT†</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.47ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dibutyl phthalate‡¶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,4'-Methoxychlor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o-Aminoazotoluene†‡¶</t>
   </si>
   <si>
     <t xml:space="preserve">5%</t>
   </si>
   <si>
+    <t xml:space="preserve">0.039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OD-PABA‡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organic UV Filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosulfuron‡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbicide (Sulfonylurea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.28ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insecticide/Pesticide (Insect Repellent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.46ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hexanoic acid</t>
+  </si>
+  <si>
     <t xml:space="preserve">35%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethyl butyrate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48ᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.19ᵃᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.29ᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benz(a)anthracene†‡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.30ᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.17ᵃᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.48ᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-MeFOSAA†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07ᵃᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.45ᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38ᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terbuthylazine‡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbicide (Triazine)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDA†‡¶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEEP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insecticide/Pesticide (Organophosphate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09ᵃᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36ᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-NOT†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.47ᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21ᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dibutyl phthalate‡¶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,4'-Methoxychlor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o-Aminoazotoluene†‡¶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OD-PABA‡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organic UV Filter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prosulfuron‡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbicide (Sulfonylurea)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.28ᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46ᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insecticide/Pesticide (Insect Repellent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.46ᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23ᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hexanoic acid</t>
   </si>
   <si>
     <t xml:space="preserve">0.042</t>
@@ -422,7 +413,7 @@
     <t xml:space="preserve">† Possible, likely, or known carcinogen
 ‡ Potential endocrine disrupting chemical
 ¶ Indicates level 2 identification
-Abbreviations: 5-NOT = 5-Nitro-o-toluidine; DEET = N,N-Diethyl-meta-toluamide; DNOP = Di-n-octyl phthalate; MDA = 4,4'-Diaminodiphenylmethane; MEHP = Mono-2-ethylhexyl phthalate; N-MeFOSAA = N-Methylperfluoro-1-octanesulfonamidoacetic acid (linear); OD-PABA = Octyl-dimethyl-p-aminobenzoic acid; PAH = polycyclic aromatic hydrocarbon; TEEP = Tetraethyl ethylenediphosphonate; TTBNP = Tris(tribromoneopentyl); UV = ultraviolet</t>
+Abbreviations: 5-NOT = 5-Nitro-o-toluidine; DEET = N,N-Diethyl-meta-toluamide; DNOP = Di-n-octyl phthalate; MDA = 4,4'-Diaminodiphenylmethane; MEHP = Mono-2-ethylhexyl phthalate; N-MeFOSAA = N-Methylperfluoro-1-octanesulfonamidoacetic acid (linear); OD-PABA = Octyl-dimethyl-p-aminobenzoic acid; PAH = polycyclic aromatic hydrocarbon; TEEP = Tetraethyl ethylenediphosphonate; UV = ultraviolet</t>
   </si>
 </sst>
 </file>
@@ -1078,10 +1069,10 @@
         <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>69</v>
@@ -1098,7 +1089,7 @@
         <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>73</v>
@@ -1118,76 +1109,76 @@
         <v>77</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>91</v>
@@ -1198,119 +1189,119 @@
         <v>92</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="E20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="D25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26">
@@ -1324,13 +1315,13 @@
         <v>111</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>112</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27">
@@ -1338,124 +1329,104 @@
         <v>113</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" ht="100" customHeight="1">
+      <c r="A32" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" ht="100" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Outputs/Tables/T3.xlsx
+++ b/Outputs/Tables/T3.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t xml:space="preserve">Chemical Name</t>
   </si>
@@ -146,6 +146,9 @@
     <t xml:space="preserve">-0.50ᵇ</t>
   </si>
   <si>
+    <t xml:space="preserve">0.010</t>
+  </si>
+  <si>
     <t xml:space="preserve">Acetophenone</t>
   </si>
   <si>
@@ -290,6 +293,15 @@
     <t xml:space="preserve">0.031</t>
   </si>
   <si>
+    <t xml:space="preserve">Dibutyl phthalate‡¶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.035</t>
+  </si>
+  <si>
     <t xml:space="preserve">5-NOT†</t>
   </si>
   <si>
@@ -299,19 +311,10 @@
     <t xml:space="preserve">0.21ᵃ</t>
   </si>
   <si>
-    <t xml:space="preserve">0.035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dibutyl phthalate‡¶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45%</t>
+    <t xml:space="preserve">0.036</t>
   </si>
   <si>
     <t xml:space="preserve">2,4'-Methoxychlor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.036</t>
   </si>
   <si>
     <t xml:space="preserve">o-Aminoazotoluene†‡¶</t>
@@ -961,18 +964,18 @@
         <v>43</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
@@ -981,72 +984,72 @@
         <v>26</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -1058,95 +1061,95 @@
         <v>26</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>13</v>
@@ -1161,44 +1164,44 @@
         <v>9</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>95</v>
@@ -1209,24 +1212,24 @@
         <v>96</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -1246,13 +1249,13 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
@@ -1261,15 +1264,15 @@
         <v>9</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>8</v>
@@ -1281,132 +1284,132 @@
         <v>16</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1416,7 +1419,7 @@
     </row>
     <row r="32" ht="100" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>

--- a/Outputs/Tables/T3.xlsx
+++ b/Outputs/Tables/T3.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">PTC</t>
   </si>
   <si>
-    <t xml:space="preserve">P value</t>
+    <t xml:space="preserve">P</t>
   </si>
   <si>
     <t xml:space="preserve">Ethylan</t>
@@ -68,6 +68,21 @@
     <t xml:space="preserve">0.005</t>
   </si>
   <si>
+    <t xml:space="preserve">3-Hydroxycarbofuran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insecticide/Pesticide (Carbamate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.007</t>
+  </si>
+  <si>
     <t xml:space="preserve">o-Toluidine†</t>
   </si>
   <si>
@@ -83,21 +98,6 @@
     <t xml:space="preserve">0.26ᵃ</t>
   </si>
   <si>
-    <t xml:space="preserve">0.007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-Hydroxycarbofuran</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insecticide/Pesticide (Carbamate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20%</t>
-  </si>
-  <si>
     <t xml:space="preserve">DNOP‡</t>
   </si>
   <si>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">0.027</t>
   </si>
   <si>
-    <t xml:space="preserve">Benz(a)anthracene†‡</t>
+    <t xml:space="preserve">Benz[a]anthracene†‡</t>
   </si>
   <si>
     <t xml:space="preserve">-0.30ᵇ</t>
@@ -314,7 +314,40 @@
     <t xml:space="preserve">0.036</t>
   </si>
   <si>
-    <t xml:space="preserve">2,4'-Methoxychlor</t>
+    <t xml:space="preserve">2,4′-Methoxychlor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OD-PABA‡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organic UV Filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosulfuron‡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbicide (Sulfonylurea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.28ᵇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insecticide/Pesticide (Insect Repellent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.46ᵃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.23ᵃ</t>
   </si>
   <si>
     <t xml:space="preserve">o-Aminoazotoluene†‡¶</t>
@@ -323,39 +356,6 @@
     <t xml:space="preserve">5%</t>
   </si>
   <si>
-    <t xml:space="preserve">0.039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OD-PABA‡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organic UV Filter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prosulfuron‡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbicide (Sulfonylurea)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.28ᵇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46ᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insecticide/Pesticide (Insect Repellent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.46ᵃ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23ᵃ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hexanoic acid</t>
   </si>
   <si>
@@ -414,9 +414,10 @@
   </si>
   <si>
     <t xml:space="preserve">† Possible, likely, or known carcinogen
-‡ Potential endocrine disrupting chemical
-¶ Indicates level 2 identification
-Abbreviations: 5-NOT = 5-Nitro-o-toluidine; DEET = N,N-Diethyl-meta-toluamide; DNOP = Di-n-octyl phthalate; MDA = 4,4'-Diaminodiphenylmethane; MEHP = Mono-2-ethylhexyl phthalate; N-MeFOSAA = N-Methylperfluoro-1-octanesulfonamidoacetic acid (linear); OD-PABA = Octyl-dimethyl-p-aminobenzoic acid; PAH = polycyclic aromatic hydrocarbon; TEEP = Tetraethyl ethylenediphosphonate; UV = ultraviolet</t>
+‡ Potential endocrine-disrupting chemical
+¶ Indicates Level 2 identification
+‖ Unadjusted P-values are displayed; none remained significant after FDR correction.
+Abbreviations: 5-NOT = 5-nitro-o-toluidine; DEET = N,N-diethyl-meta-toluamide; DNOP = di-n-octyl phthalate; FDR = false discovery rate; MDA = 4,4′-diaminodiphenylmethane; MEHP = mono(2-ethylhexyl) phthalate; N-MeFOSAA = N-methylperfluoro-1-octanesulfonamidoacetic acid (linear); OD-PABA = octyl-dimethyl-p-aminobenzoic acid; PAH = polycyclic aromatic hydrocarbon; PFAS = per- and polyfluoroalkyl substances; TEEP = tetraethyl ethylenediphosphonate; UV = ultraviolet</t>
   </si>
 </sst>
 </file>
@@ -424,7 +425,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -446,13 +447,19 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <i/>
     </font>
     <font>
       <sz val="7.5"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <b/>
+    </font>
+    <font>
+      <sz val="7.5"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <b/>
+      <i/>
     </font>
   </fonts>
   <fills count="3">
@@ -493,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -508,7 +515,12 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -823,7 +835,7 @@
       <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -875,27 +887,27 @@
         <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>26</v>
@@ -904,7 +916,7 @@
         <v>27</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -981,7 +993,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>48</v>
@@ -1055,10 +1067,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>66</v>
@@ -1158,7 +1170,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>9</v>
@@ -1212,7 +1224,7 @@
         <v>96</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>97</v>
@@ -1221,7 +1233,7 @@
         <v>98</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>99</v>
@@ -1235,13 +1247,13 @@
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>99</v>
@@ -1252,16 +1264,16 @@
         <v>101</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>103</v>
@@ -1275,13 +1287,13 @@
         <v>105</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>103</v>
@@ -1289,19 +1301,19 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>103</v>
@@ -1309,19 +1321,19 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>103</v>

--- a/Outputs/Tables/T3.xlsx
+++ b/Outputs/Tables/T3.xlsx
@@ -413,11 +413,11 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">† Possible, likely, or known carcinogen
+    <t xml:space="preserve">† Known, likely, or possible carcinogen
 ‡ Potential endocrine-disrupting chemical
 ¶ Indicates Level 2 identification
 ‖ Unadjusted P-values are displayed; none remained significant after FDR correction.
-Abbreviations: 5-NOT = 5-nitro-o-toluidine; DEET = N,N-diethyl-meta-toluamide; DNOP = di-n-octyl phthalate; FDR = false discovery rate; MDA = 4,4′-diaminodiphenylmethane; MEHP = mono(2-ethylhexyl) phthalate; N-MeFOSAA = N-methylperfluoro-1-octanesulfonamidoacetic acid (linear); OD-PABA = octyl-dimethyl-p-aminobenzoic acid; PAH = polycyclic aromatic hydrocarbon; PFAS = per- and polyfluoroalkyl substances; TEEP = tetraethyl ethylenediphosphonate; UV = ultraviolet</t>
+Abbreviations: 5-NOT = 5-nitro-o-toluidine; DEET = N,N-diethyl-meta-toluamide; DNOP = di-n-octyl phthalate; FDR = false discovery rate; FTC = follicular thyroid carcinoma; IEFVPTC = invasive encapsulated follicular variant of papillary thyroid carcinoma; MDA = 4,4′-diaminodiphenylmethane; MEHP = mono(2-ethylhexyl) phthalate; N-MeFOSAA = N-methylperfluoro-1-octanesulfonamidoacetic acid (linear); OD-PABA = octyl-dimethyl-p-aminobenzoic acid; PAH = polycyclic aromatic hydrocarbon; PFAS = per- and polyfluoroalkyl substances; PTC = papillary thyroid carcinoma; TEEP = tetraethyl ethylenediphosphonate; UV = ultraviolet</t>
   </si>
 </sst>
 </file>
